--- a/LATEST_SCHEMA/schema_dbo_mssql.xlsx
+++ b/LATEST_SCHEMA/schema_dbo_mssql.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13"/>
@@ -826,15 +826,15 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="51" customWidth="1" min="11" max="11"/>
-    <col width="63" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
@@ -891,50 +891,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>primary_keys</t>
+          <t>table_description</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>incremental_columns</t>
+          <t>classification_summary_json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns</t>
+          <t>unit_summary_json</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns_candidates</t>
+          <t>row_count_projection_1y</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>table_description</t>
+          <t>row_count_projection_2y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>classification_summary_json</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>unit_summary_json</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_1y</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_2y</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -971,47 +951,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>po_id</t>
+          <t>Procurement headers including approver employee relationship.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>order_date, expected_date, created_at, updated_at</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Procurement headers including approver employee relationship.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>155</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>185</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>276</v>
       </c>
     </row>
@@ -1045,10 +1009,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1090,10 +1050,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1161,10 +1117,6 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1206,10 +1158,6 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1289,10 +1237,6 @@
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n"/>
-      <c r="Q27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2539,18 +2483,18 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2559,7 +2503,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -2738,15 +2682,15 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="63" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
@@ -2803,50 +2747,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>primary_keys</t>
+          <t>table_description</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>incremental_columns</t>
+          <t>classification_summary_json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns</t>
+          <t>unit_summary_json</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns_candidates</t>
+          <t>row_count_projection_1y</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>table_description</t>
+          <t>row_count_projection_2y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>classification_summary_json</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>unit_summary_json</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_1y</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_2y</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -2883,47 +2807,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>sales_order_item_id</t>
+          <t>Sales line items with sold quantity and explicit unit labels.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>created_at, updated_at</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Sales line items with sold quantity and explicit unit labels.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>508</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>508</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>508</v>
       </c>
     </row>
@@ -2957,10 +2865,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3002,10 +2906,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3061,10 +2961,6 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3106,10 +3002,6 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3169,10 +3061,6 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4327,18 +4215,18 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4347,7 +4235,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4634,15 +4522,15 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="69" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
     <col width="67" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
@@ -4699,50 +4587,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>primary_keys</t>
+          <t>table_description</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>incremental_columns</t>
+          <t>classification_summary_json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns</t>
+          <t>unit_summary_json</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns_candidates</t>
+          <t>row_count_projection_1y</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>table_description</t>
+          <t>row_count_projection_2y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>classification_summary_json</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>unit_summary_json</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_1y</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_2y</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -4779,47 +4647,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>sales_order_id</t>
+          <t>Sales headers including assigned sales representative relationship.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>order_date, created_at, updated_at</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Sales headers including assigned sales representative relationship.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>242</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>284</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>412</v>
       </c>
     </row>
@@ -4853,10 +4705,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4898,10 +4746,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4981,10 +4825,6 @@
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5026,10 +4866,6 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5099,10 +4935,6 @@
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n"/>
-      <c r="Q27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6453,18 +6285,18 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6473,7 +6305,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6652,15 +6484,15 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
@@ -6717,50 +6549,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>primary_keys</t>
+          <t>table_description</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>incremental_columns</t>
+          <t>classification_summary_json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns</t>
+          <t>unit_summary_json</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns_candidates</t>
+          <t>row_count_projection_1y</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>table_description</t>
+          <t>row_count_projection_2y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>classification_summary_json</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>unit_summary_json</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_1y</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_2y</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -6797,43 +6609,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>store_id</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>created_at, updated_at</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>17</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>29</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>65</v>
       </c>
     </row>
@@ -6867,10 +6663,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -6912,10 +6704,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6957,10 +6745,6 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8575,18 +8359,18 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -8595,7 +8379,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -8708,15 +8492,15 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
@@ -8773,50 +8557,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>primary_keys</t>
+          <t>table_description</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>incremental_columns</t>
+          <t>classification_summary_json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns</t>
+          <t>unit_summary_json</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns_candidates</t>
+          <t>row_count_projection_1y</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>table_description</t>
+          <t>row_count_projection_2y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>classification_summary_json</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>unit_summary_json</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_1y</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_2y</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -8853,43 +8617,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>supplier_id</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>created_at, updated_at</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>22</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>35</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>74</v>
       </c>
     </row>
@@ -8923,10 +8671,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8968,10 +8712,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9013,10 +8753,6 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10071,18 +9807,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -10091,7 +9827,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -10271,7 +10007,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"metadata":{"generated_at":"2026-03-12T15:25:12.285698+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes&amp;timeout=30","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":""},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"LastName1","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit s</t>
+          <t>{"metadata":{"generated_at":"2026-03-16T14:06:08.466941+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":""},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":18,"info":46,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"LastName1","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":true,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"info","detail":"No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.","recommendation":"Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.","delete_strategy":"hard_delete_with_cdc","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":true,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"info","detail":"No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.","recommendation":"Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.","delete_strategy":"hard_delete_with_cdc","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":true,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"info","detail":"No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.","recommendation":"Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.","delete_strategy":"hard_delete_with_cdc","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discre</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10017,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ource unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detai</t>
+          <t>te","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":true,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":true,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"info","detail":"No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.","recommendation":"Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.","delete_strategy":"hard_delete_with_cdc","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":true,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"info","detail":"No soft-delete column found, but CDC is ena</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10027,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>l":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column"</t>
+          <t>bled. Hard deletes can be captured via change data capture.","recommendation":"Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.","delete_strategy":"hard_delete_with_cdc","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":true,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"info","detail":"No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.","recommendation":"Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.","delete_strategy":"hard_delete_with_cdc","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":true,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"info","detail":"No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.","recommendation":"Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.","delete_strategy":"hard_delete_with_cdc","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":true,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"info","detail":"No soft-delete column foun</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10037,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>:"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
+          <t>d, but CDC is enabled. Hard deletes can be captured via change data capture.","recommendation":"Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.","delete_strategy":"hard_delete_with_cdc","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":true,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"info","detail":"No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.","recommendation":"Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.","delete_strategy":"hard_delete_with_cdc","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10097,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-03-12T15:25:12.285698+00:00</t>
+          <t>2026-03-16T14:06:08.466941+00:00</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -10376,7 +10112,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes&amp;timeout=30</t>
+          <t>pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes</t>
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -11072,7 +10808,7 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
@@ -11415,18 +11151,18 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -11435,7 +11171,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -11669,18 +11405,18 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -11689,7 +11425,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -11983,18 +11719,18 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -12003,7 +11739,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -12787,18 +12523,18 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -12807,7 +12543,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -13273,18 +13009,18 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -13293,7 +13029,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -13529,18 +13265,18 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -13549,7 +13285,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -14015,18 +13751,18 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -14035,7 +13771,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -14753,18 +14489,18 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -14773,7 +14509,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -15059,18 +14795,18 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -15079,7 +14815,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -15404,15 +15140,15 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
@@ -15469,50 +15205,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>primary_keys</t>
+          <t>table_description</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>incremental_columns</t>
+          <t>classification_summary_json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns</t>
+          <t>unit_summary_json</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns_candidates</t>
+          <t>row_count_projection_1y</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>table_description</t>
+          <t>row_count_projection_2y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>classification_summary_json</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>unit_summary_json</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_1y</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_2y</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -15549,43 +15265,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>created_at, updated_at</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>126</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>152</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>232</v>
       </c>
     </row>
@@ -15619,10 +15319,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -15664,10 +15360,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -15709,10 +15401,6 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -16791,18 +16479,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -16811,7 +16499,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -16924,15 +16612,15 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
@@ -16989,50 +16677,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>primary_keys</t>
+          <t>table_description</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>incremental_columns</t>
+          <t>classification_summary_json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns</t>
+          <t>unit_summary_json</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns_candidates</t>
+          <t>row_count_projection_1y</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>table_description</t>
+          <t>row_count_projection_2y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>classification_summary_json</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>unit_summary_json</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_1y</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_2y</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -17069,43 +16737,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>employee_id</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>hire_date, created_at, updated_at</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>35</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>50</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>96</v>
       </c>
     </row>
@@ -17139,10 +16791,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -17184,10 +16832,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17231,10 +16875,6 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17276,10 +16916,6 @@
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17349,10 +16985,6 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -18517,18 +18149,18 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -18537,7 +18169,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -18716,15 +18348,15 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="43" customWidth="1" min="11" max="11"/>
-    <col width="65" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
@@ -18781,50 +18413,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>primary_keys</t>
+          <t>table_description</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>incremental_columns</t>
+          <t>classification_summary_json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns</t>
+          <t>unit_summary_json</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns_candidates</t>
+          <t>row_count_projection_1y</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>table_description</t>
+          <t>row_count_projection_2y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>classification_summary_json</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>unit_summary_json</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_1y</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_2y</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -18861,47 +18473,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>inventory_id</t>
+          <t>Current stock levels with normalized stock unit representation.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>last_restocked_at, created_at, updated_at</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Current stock levels with normalized stock unit representation.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>146</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>193</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>334</v>
       </c>
     </row>
@@ -18935,10 +18531,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -18980,10 +18572,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19039,10 +18627,6 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -19084,10 +18668,6 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19157,10 +18737,6 @@
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
-      <c r="P25" s="2" t="n"/>
-      <c r="Q25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20375,18 +19951,18 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -20395,7 +19971,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -20566,15 +20142,15 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="80" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
@@ -20631,50 +20207,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>primary_keys</t>
+          <t>table_description</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>incremental_columns</t>
+          <t>classification_summary_json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns</t>
+          <t>unit_summary_json</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns_candidates</t>
+          <t>row_count_projection_1y</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>table_description</t>
+          <t>row_count_projection_2y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>classification_summary_json</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>unit_summary_json</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_1y</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_2y</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -20711,47 +20267,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>product_id</t>
+          <t>Master product catalog including physical units for analyzer unit-context testing.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>created_at, updated_at</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Master product catalog including physical units for analyzer unit-context testing.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>68</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>86</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>141</v>
       </c>
     </row>
@@ -20785,10 +20325,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -20830,10 +20366,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20889,10 +20421,6 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20934,10 +20462,6 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20997,10 +20521,6 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23120,15 +22640,15 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="80" customWidth="1" min="20" max="20"/>
@@ -23185,50 +22705,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>primary_keys</t>
+          <t>table_description</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>incremental_columns</t>
+          <t>classification_summary_json</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns</t>
+          <t>unit_summary_json</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>partition_columns_candidates</t>
+          <t>row_count_projection_1y</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>table_description</t>
+          <t>row_count_projection_2y</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>classification_summary_json</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>unit_summary_json</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_1y</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>row_count_projection_2y</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>row_count_projection_5y</t>
         </is>
@@ -23265,47 +22765,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>po_item_id</t>
+          <t>Line items with order quantities and explicit unit labels.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>created_at, updated_at</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Line items with order quantities and explicit unit labels.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>246</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>246</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>246</v>
       </c>
     </row>
@@ -23339,10 +22823,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -23384,10 +22864,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23443,10 +22919,6 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -23488,10 +22960,6 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -23551,10 +23019,6 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -24709,18 +24173,18 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.</t>
+          <t>No soft-delete column found, but CDC is enabled. Hard deletes can be captured via change data capture.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE … REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.</t>
+          <t>Use CDC (e.g. Debezium, pgoutput) to capture DELETE events.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -24729,7 +24193,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>hard_delete</t>
+          <t>hard_delete_with_cdc</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
